--- a/data/definition.xlsx
+++ b/data/definition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucel\Documents\PythonStudy\AirlineProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85AC4A51-52C0-4ECD-B177-63A6BE7E8BC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC7465A-2969-468B-835C-BD99D3796BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="18195" xr2:uid="{0B64C66F-2FC4-45E2-896F-20A02B7860B9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="646" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="110">
   <si>
     <t>リードタイム</t>
     <phoneticPr fontId="2"/>
@@ -1011,6 +1011,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1037,9 +1040,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1324,43 +1324,38 @@
   <dimension ref="A1:AX43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.9375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="11.25" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="9.3125" style="1" customWidth="1"/>
-    <col min="15" max="15" width="12.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="12.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.5" style="1" customWidth="1"/>
+    <col min="1" max="2" width="12.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="9.4375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="12.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="9.4375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="12.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="18" width="12.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="9.4375" style="1" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.3125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="12.4375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="9.625" style="1" customWidth="1"/>
-    <col min="25" max="25" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="9.625" style="1" customWidth="1"/>
-    <col min="30" max="30" width="13.8125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.4375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="9.625" style="1" customWidth="1"/>
-    <col min="35" max="35" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="38" width="12.5625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="12.5625" style="1" customWidth="1"/>
-    <col min="40" max="40" width="12.5625" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="9.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="9.4375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="12.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="9.4375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="10.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="9.4375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="9.4375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="9.4375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="10.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="39" width="12.375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="10.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="42" width="15.5625" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="43" width="9.4375" style="1" bestFit="1" customWidth="1"/>
     <col min="44" max="44" width="15.5625" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="47" width="15.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="10.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="45" max="45" width="10.3125" style="1" bestFit="1" customWidth="1"/>
+    <col min="46" max="47" width="15.5625" style="1" bestFit="1" customWidth="1"/>
+    <col min="48" max="48" width="9.9375" style="1" bestFit="1" customWidth="1"/>
     <col min="49" max="49" width="15.5625" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="15.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="50" max="50" width="10.3125" style="1" bestFit="1" customWidth="1"/>
     <col min="51" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1374,55 +1369,55 @@
       <c r="K1" s="46" t="s">
         <v>89</v>
       </c>
-      <c r="P1" s="54" t="s">
+      <c r="P1" s="55" t="s">
         <v>88</v>
       </c>
-      <c r="Q1" s="55"/>
-      <c r="R1" s="55"/>
-      <c r="S1" s="55"/>
-      <c r="T1" s="55"/>
-      <c r="U1" s="52" t="s">
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
+      <c r="S1" s="56"/>
+      <c r="T1" s="56"/>
+      <c r="U1" s="53" t="s">
         <v>87</v>
       </c>
-      <c r="V1" s="53"/>
-      <c r="W1" s="53"/>
-      <c r="X1" s="53"/>
-      <c r="Y1" s="53"/>
-      <c r="Z1" s="56" t="s">
+      <c r="V1" s="54"/>
+      <c r="W1" s="54"/>
+      <c r="X1" s="54"/>
+      <c r="Y1" s="54"/>
+      <c r="Z1" s="57" t="s">
         <v>86</v>
       </c>
-      <c r="AA1" s="57"/>
-      <c r="AB1" s="57"/>
-      <c r="AC1" s="57"/>
-      <c r="AD1" s="57"/>
-      <c r="AE1" s="58" t="s">
+      <c r="AA1" s="58"/>
+      <c r="AB1" s="58"/>
+      <c r="AC1" s="58"/>
+      <c r="AD1" s="58"/>
+      <c r="AE1" s="59" t="s">
         <v>85</v>
       </c>
-      <c r="AF1" s="57"/>
-      <c r="AG1" s="57"/>
-      <c r="AH1" s="57"/>
-      <c r="AI1" s="57"/>
-      <c r="AJ1" s="59" t="s">
+      <c r="AF1" s="58"/>
+      <c r="AG1" s="58"/>
+      <c r="AH1" s="58"/>
+      <c r="AI1" s="58"/>
+      <c r="AJ1" s="60" t="s">
         <v>84</v>
       </c>
-      <c r="AK1" s="59"/>
-      <c r="AL1" s="59"/>
-      <c r="AM1" s="59"/>
-      <c r="AN1" s="59"/>
-      <c r="AO1" s="52" t="s">
+      <c r="AK1" s="60"/>
+      <c r="AL1" s="60"/>
+      <c r="AM1" s="60"/>
+      <c r="AN1" s="60"/>
+      <c r="AO1" s="53" t="s">
         <v>83</v>
       </c>
-      <c r="AP1" s="53"/>
-      <c r="AQ1" s="53"/>
-      <c r="AR1" s="60"/>
-      <c r="AS1" s="60"/>
-      <c r="AT1" s="52" t="s">
+      <c r="AP1" s="54"/>
+      <c r="AQ1" s="54"/>
+      <c r="AR1" s="61"/>
+      <c r="AS1" s="61"/>
+      <c r="AT1" s="53" t="s">
         <v>82</v>
       </c>
-      <c r="AU1" s="53"/>
-      <c r="AV1" s="53"/>
-      <c r="AW1" s="53"/>
-      <c r="AX1" s="53"/>
+      <c r="AU1" s="54"/>
+      <c r="AV1" s="54"/>
+      <c r="AW1" s="54"/>
+      <c r="AX1" s="54"/>
     </row>
     <row r="2" spans="1:50" ht="168.75" customHeight="1" thickTop="1" thickBot="1">
       <c r="A2" s="45" t="s">
@@ -1724,8 +1719,8 @@
       <c r="AW3" s="30" t="s">
         <v>39</v>
       </c>
-      <c r="AX3" s="30" t="s">
-        <v>39</v>
+      <c r="AX3" s="33" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="4" spans="1:50" ht="15.4" thickBot="1">
@@ -1997,9 +1992,7 @@
       <c r="AF6" s="16"/>
       <c r="AG6" s="16"/>
       <c r="AH6" s="15"/>
-      <c r="AI6" s="15" t="s">
-        <v>35</v>
-      </c>
+      <c r="AI6" s="15"/>
       <c r="AJ6" s="9"/>
       <c r="AK6" s="8"/>
       <c r="AL6" s="8"/>
@@ -2009,9 +2002,7 @@
       <c r="AP6" s="14"/>
       <c r="AQ6" s="14"/>
       <c r="AR6" s="11"/>
-      <c r="AS6" s="15" t="s">
-        <v>35</v>
-      </c>
+      <c r="AS6" s="15"/>
       <c r="AT6" s="13" t="s">
         <v>35</v>
       </c>
@@ -2297,7 +2288,7 @@
       <c r="Z10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="AA10" s="61" t="s">
+      <c r="AA10" s="52" t="s">
         <v>32</v>
       </c>
       <c r="AB10" s="14"/>
@@ -2359,9 +2350,7 @@
         <v>31</v>
       </c>
       <c r="AB11" s="12"/>
-      <c r="AC11" s="11" t="s">
-        <v>31</v>
-      </c>
+      <c r="AC11" s="11"/>
       <c r="AD11" s="7"/>
       <c r="AE11" s="9"/>
       <c r="AF11" s="8"/>
@@ -2417,9 +2406,7 @@
         <v>30</v>
       </c>
       <c r="AB12" s="12"/>
-      <c r="AC12" s="11" t="s">
-        <v>30</v>
-      </c>
+      <c r="AC12" s="11"/>
       <c r="AD12" s="7"/>
       <c r="AE12" s="9"/>
       <c r="AF12" s="8"/>
@@ -2870,39 +2857,27 @@
       <c r="A18" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="19" t="s">
-        <v>24</v>
-      </c>
+      <c r="B18" s="15"/>
       <c r="C18" s="19"/>
-      <c r="D18" s="15" t="s">
-        <v>24</v>
-      </c>
+      <c r="D18" s="15"/>
       <c r="E18" s="15" t="s">
         <v>24</v>
       </c>
       <c r="F18" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="G18" s="19" t="s">
-        <v>24</v>
-      </c>
+      <c r="G18" s="15"/>
       <c r="H18" s="16"/>
-      <c r="I18" s="15" t="s">
-        <v>24</v>
-      </c>
+      <c r="I18" s="15"/>
       <c r="J18" s="15" t="s">
         <v>24</v>
       </c>
       <c r="K18" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="L18" s="19" t="s">
-        <v>24</v>
-      </c>
+      <c r="L18" s="15"/>
       <c r="M18" s="19"/>
-      <c r="N18" s="15" t="s">
-        <v>24</v>
-      </c>
+      <c r="N18" s="15"/>
       <c r="O18" s="15" t="s">
         <v>24</v>
       </c>
@@ -3404,7 +3379,9 @@
       <c r="A25" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B25" s="16"/>
+      <c r="B25" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="C25" s="18" t="s">
         <v>16</v>
       </c>
@@ -3417,7 +3394,9 @@
       <c r="F25" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="G25" s="16"/>
+      <c r="G25" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="H25" s="18" t="s">
         <v>16</v>
       </c>
@@ -3430,7 +3409,9 @@
       <c r="K25" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="L25" s="16"/>
+      <c r="L25" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="M25" s="18" t="s">
         <v>16</v>
       </c>
@@ -3443,7 +3424,9 @@
       <c r="P25" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="Q25" s="16"/>
+      <c r="Q25" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="R25" s="18" t="s">
         <v>16</v>
       </c>
@@ -3456,7 +3439,9 @@
       <c r="U25" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="V25" s="14"/>
+      <c r="V25" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="W25" s="20" t="s">
         <v>16</v>
       </c>
@@ -3469,7 +3454,9 @@
       <c r="Z25" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="AA25" s="14"/>
+      <c r="AA25" s="17" t="s">
+        <v>16</v>
+      </c>
       <c r="AB25" s="20" t="s">
         <v>16</v>
       </c>
@@ -3503,7 +3490,9 @@
       <c r="AT25" s="13" t="s">
         <v>16</v>
       </c>
-      <c r="AU25" s="14"/>
+      <c r="AU25" s="12" t="s">
+        <v>16</v>
+      </c>
       <c r="AV25" s="20" t="s">
         <v>16</v>
       </c>
@@ -3516,7 +3505,9 @@
       <c r="A26" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="B26" s="16"/>
+      <c r="B26" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="C26" s="18" t="s">
         <v>15</v>
       </c>
@@ -3529,7 +3520,9 @@
       <c r="F26" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="G26" s="16"/>
+      <c r="G26" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="H26" s="18" t="s">
         <v>15</v>
       </c>
@@ -3542,7 +3535,9 @@
       <c r="K26" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="L26" s="16"/>
+      <c r="L26" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="M26" s="18" t="s">
         <v>15</v>
       </c>
@@ -3555,7 +3550,9 @@
       <c r="P26" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="Q26" s="16"/>
+      <c r="Q26" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="R26" s="18" t="s">
         <v>15</v>
       </c>
@@ -3568,7 +3565,9 @@
       <c r="U26" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="V26" s="14"/>
+      <c r="V26" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="W26" s="20" t="s">
         <v>15</v>
       </c>
@@ -3581,7 +3580,9 @@
       <c r="Z26" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="AA26" s="14"/>
+      <c r="AA26" s="17" t="s">
+        <v>15</v>
+      </c>
       <c r="AB26" s="20" t="s">
         <v>15</v>
       </c>
@@ -3615,7 +3616,9 @@
       <c r="AT26" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="AU26" s="14"/>
+      <c r="AU26" s="12" t="s">
+        <v>15</v>
+      </c>
       <c r="AV26" s="20" t="s">
         <v>15</v>
       </c>
@@ -4441,9 +4444,7 @@
         <v>3</v>
       </c>
       <c r="AB37" s="12"/>
-      <c r="AC37" s="11" t="s">
-        <v>3</v>
-      </c>
+      <c r="AC37" s="11"/>
       <c r="AD37" s="7"/>
       <c r="AE37" s="9"/>
       <c r="AF37" s="8"/>

--- a/data/definition.xlsx
+++ b/data/definition.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lucel\Documents\PythonStudy\AirlineProject\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BC7465A-2969-468B-835C-BD99D3796BA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B526FB96-4028-42DD-A8BF-EA1A8007498D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28702" yWindow="-98" windowWidth="28995" windowHeight="18195" xr2:uid="{0B64C66F-2FC4-45E2-896F-20A02B7860B9}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="649" uniqueCount="111">
   <si>
     <t>リードタイム</t>
     <phoneticPr fontId="2"/>
@@ -463,6 +463,10 @@
   </si>
   <si>
     <t>REINDEXED_COLUMNS9</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>搭乗手続開始時刻</t>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -888,7 +892,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1041,6 +1045,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -1321,7 +1326,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E52CC792-F8BB-4F84-B37C-9CF14FC90512}">
-  <dimension ref="A1:AX43"/>
+  <dimension ref="A1:AX44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="12.3125" style="1" bestFit="1" customWidth="1"/>
@@ -4645,191 +4650,243 @@
       <c r="AW40" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="AX40" s="48" t="s">
-        <v>0</v>
-      </c>
+      <c r="AX40" s="48"/>
     </row>
     <row r="41" spans="1:50" ht="15.75" thickTop="1" thickBot="1">
-      <c r="A41" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="D41" s="15"/>
-      <c r="E41" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="F41" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="G41" s="16"/>
-      <c r="H41" s="16"/>
-      <c r="I41" s="15"/>
-      <c r="J41" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="K41" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="L41" s="16"/>
-      <c r="M41" s="16"/>
-      <c r="N41" s="15"/>
-      <c r="O41" s="15" t="s">
-        <v>99</v>
-      </c>
-      <c r="P41" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q41" s="16"/>
-      <c r="R41" s="16"/>
-      <c r="S41" s="15"/>
-      <c r="T41" s="15"/>
-      <c r="U41" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="V41" s="14"/>
-      <c r="W41" s="14"/>
-      <c r="X41" s="11"/>
-      <c r="Y41" s="11"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="8"/>
+      <c r="C41" s="8"/>
+      <c r="D41" s="7"/>
+      <c r="E41" s="7"/>
+      <c r="F41" s="9"/>
+      <c r="G41" s="8"/>
+      <c r="H41" s="8"/>
+      <c r="I41" s="7"/>
+      <c r="J41" s="7"/>
+      <c r="K41" s="9"/>
+      <c r="L41" s="8"/>
+      <c r="M41" s="8"/>
+      <c r="N41" s="7"/>
+      <c r="O41" s="7"/>
+      <c r="P41" s="9"/>
+      <c r="Q41" s="8"/>
+      <c r="R41" s="8"/>
+      <c r="S41" s="7"/>
+      <c r="T41" s="7"/>
+      <c r="U41" s="5"/>
+      <c r="V41" s="62"/>
+      <c r="W41" s="62"/>
+      <c r="X41" s="62"/>
+      <c r="Y41" s="62"/>
       <c r="Z41" s="5"/>
-      <c r="AA41" s="2"/>
-      <c r="AB41" s="2"/>
-      <c r="AC41" s="6"/>
-      <c r="AD41" s="15"/>
-      <c r="AE41" s="17"/>
-      <c r="AF41" s="16"/>
-      <c r="AG41" s="16"/>
-      <c r="AH41" s="15"/>
-      <c r="AI41" s="15"/>
-      <c r="AJ41" s="9"/>
+      <c r="AA41" s="62"/>
+      <c r="AB41" s="62"/>
+      <c r="AC41" s="62"/>
+      <c r="AD41" s="7"/>
+      <c r="AE41" s="46"/>
+      <c r="AF41" s="8"/>
+      <c r="AG41" s="8"/>
+      <c r="AH41" s="7"/>
+      <c r="AI41" s="7"/>
+      <c r="AJ41" s="46"/>
       <c r="AK41" s="8"/>
       <c r="AL41" s="8"/>
       <c r="AM41" s="7"/>
       <c r="AN41" s="7"/>
-      <c r="AO41" s="13"/>
-      <c r="AP41" s="14"/>
-      <c r="AQ41" s="14"/>
-      <c r="AR41" s="11"/>
-      <c r="AS41" s="15"/>
+      <c r="AO41" s="5"/>
+      <c r="AP41" s="2"/>
+      <c r="AQ41" s="2"/>
+      <c r="AR41" s="6"/>
+      <c r="AS41" s="7"/>
       <c r="AT41" s="5"/>
-      <c r="AU41" s="2"/>
-      <c r="AV41" s="2"/>
+      <c r="AU41" s="4"/>
+      <c r="AV41" s="4"/>
       <c r="AW41" s="2"/>
-      <c r="AX41" s="48"/>
+      <c r="AX41" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="42" spans="1:50" ht="15.75" thickTop="1" thickBot="1">
       <c r="A42" s="17" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
-      <c r="D42" s="15" t="s">
-        <v>4</v>
-      </c>
+      <c r="D42" s="15"/>
       <c r="E42" s="15" t="s">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="F42" s="17" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G42" s="16"/>
       <c r="H42" s="16"/>
-      <c r="I42" s="15" t="s">
-        <v>4</v>
-      </c>
+      <c r="I42" s="15"/>
       <c r="J42" s="15" t="s">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="K42" s="17" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L42" s="16"/>
       <c r="M42" s="16"/>
-      <c r="N42" s="15" t="s">
-        <v>4</v>
-      </c>
+      <c r="N42" s="15"/>
       <c r="O42" s="15" t="s">
-        <v>4</v>
+        <v>99</v>
       </c>
       <c r="P42" s="17" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q42" s="16"/>
       <c r="R42" s="16"/>
-      <c r="S42" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="T42" s="15" t="s">
-        <v>4</v>
-      </c>
+      <c r="S42" s="15"/>
+      <c r="T42" s="15"/>
       <c r="U42" s="13" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V42" s="14"/>
       <c r="W42" s="14"/>
-      <c r="X42" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="Y42" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="Z42" s="13" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA42" s="14"/>
-      <c r="AB42" s="14"/>
-      <c r="AC42" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="AD42" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="AE42" s="17" t="s">
-        <v>4</v>
-      </c>
+      <c r="X42" s="11"/>
+      <c r="Y42" s="11"/>
+      <c r="Z42" s="5"/>
+      <c r="AA42" s="2"/>
+      <c r="AB42" s="2"/>
+      <c r="AC42" s="6"/>
+      <c r="AD42" s="15"/>
+      <c r="AE42" s="17"/>
       <c r="AF42" s="16"/>
       <c r="AG42" s="16"/>
-      <c r="AH42" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="AI42" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ42" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="AK42" s="16"/>
-      <c r="AL42" s="16"/>
-      <c r="AM42" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="AN42" s="15" t="s">
-        <v>4</v>
-      </c>
-      <c r="AO42" s="13" t="s">
-        <v>4</v>
-      </c>
+      <c r="AH42" s="15"/>
+      <c r="AI42" s="15"/>
+      <c r="AJ42" s="9"/>
+      <c r="AK42" s="8"/>
+      <c r="AL42" s="8"/>
+      <c r="AM42" s="7"/>
+      <c r="AN42" s="7"/>
+      <c r="AO42" s="13"/>
       <c r="AP42" s="14"/>
       <c r="AQ42" s="14"/>
-      <c r="AR42" s="11" t="s">
+      <c r="AR42" s="11"/>
+      <c r="AS42" s="15"/>
+      <c r="AT42" s="5"/>
+      <c r="AU42" s="2"/>
+      <c r="AV42" s="2"/>
+      <c r="AW42" s="2"/>
+      <c r="AX42" s="22"/>
+    </row>
+    <row r="43" spans="1:50" ht="15.75" thickTop="1" thickBot="1">
+      <c r="A43" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="AS42" s="15" t="s">
+      <c r="B43" s="16"/>
+      <c r="C43" s="16"/>
+      <c r="D43" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AT42" s="13" t="s">
+      <c r="E43" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="AU42" s="14"/>
-      <c r="AV42" s="14"/>
-      <c r="AW42" s="14" t="s">
+      <c r="F43" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="AX42" s="47" t="s">
+      <c r="G43" s="16"/>
+      <c r="H43" s="16"/>
+      <c r="I43" s="15" t="s">
         <v>4</v>
       </c>
+      <c r="J43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="K43" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="L43" s="16"/>
+      <c r="M43" s="16"/>
+      <c r="N43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="O43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="P43" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q43" s="16"/>
+      <c r="R43" s="16"/>
+      <c r="S43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="T43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="U43" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="V43" s="14"/>
+      <c r="W43" s="14"/>
+      <c r="X43" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="Y43" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="Z43" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA43" s="14"/>
+      <c r="AB43" s="14"/>
+      <c r="AC43" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AD43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AE43" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="AF43" s="16"/>
+      <c r="AG43" s="16"/>
+      <c r="AH43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AI43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ43" s="17" t="s">
+        <v>4</v>
+      </c>
+      <c r="AK43" s="16"/>
+      <c r="AL43" s="16"/>
+      <c r="AM43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AN43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AO43" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AP43" s="14"/>
+      <c r="AQ43" s="14"/>
+      <c r="AR43" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="AS43" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="AT43" s="13" t="s">
+        <v>4</v>
+      </c>
+      <c r="AU43" s="14"/>
+      <c r="AV43" s="14"/>
+      <c r="AW43" s="14" t="s">
+        <v>4</v>
+      </c>
+      <c r="AX43" s="47" t="s">
+        <v>4</v>
+      </c>
     </row>
-    <row r="43" spans="1:50" ht="15.4" thickTop="1"/>
+    <row r="44" spans="1:50" ht="15.4" thickTop="1"/>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="AT1:AX1"/>
